--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_41.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3232749.332098191</v>
+        <v>3269079.546583285</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>987.0883260126967</v>
+        <v>987.0883260127118</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>987.0883260126967</v>
+        <v>987.0883260127118</v>
       </c>
     </row>
     <row r="11">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>80.07191941636594</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -669,7 +669,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>1.415908396048882</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
         <v>3.769060713577687</v>
@@ -736,25 +736,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>160.712244306859</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,13 +781,13 @@
         <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.5184388018132</v>
+        <v>147.1250057391761</v>
       </c>
       <c r="S3" t="n">
-        <v>62.44885845517734</v>
+        <v>373</v>
       </c>
       <c r="T3" t="n">
-        <v>4.464774651476091</v>
+        <v>373</v>
       </c>
       <c r="U3" t="n">
         <v>0.1957842884886531</v>
@@ -906,10 +906,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.343301935257416</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.769060713577661</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.41253966161939</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8629887637398</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>251.1415773812615</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -982,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,22 +1018,22 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>133.5184388018133</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
         <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>4.46477465147608</v>
+        <v>374</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1957842884886345</v>
+        <v>374</v>
       </c>
       <c r="V6" t="n">
-        <v>191.5764578294141</v>
+        <v>245.5195491999743</v>
       </c>
       <c r="W6" t="n">
-        <v>374</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.51638189435316</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
         <v>142.7621408454554</v>
@@ -1091,7 +1091,7 @@
         <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>264.9837661807365</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
         <v>310.286266425598</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.343301935257416</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.769060713577661</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,16 +1176,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.953406460791602</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.41253966161939</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8629887637398</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.18817092047</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>140.4386267658498</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1255,16 +1255,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>292.1779336902721</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.46477465147608</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1957842884886345</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.51638189435316</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
         <v>142.7621408454554</v>
@@ -1328,7 +1328,7 @@
         <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>264.9837661807365</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
         <v>310.286266425598</v>
@@ -1386,7 +1386,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U11" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>361.0999124455193</v>
@@ -1453,16 +1453,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873973</v>
+        <v>177.6137898608468</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>305.4120422616788</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
@@ -1513,7 +1513,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1568,7 +1568,7 @@
         <v>291.4220612627038</v>
       </c>
       <c r="Q13" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
         <v>377.7099312598395</v>
@@ -1620,7 +1620,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H14" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T14" t="n">
         <v>259.6218731858503</v>
@@ -1684,10 +1684,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>200.5295027796759</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
@@ -1699,7 +1699,7 @@
         <v>3.999611346725456</v>
       </c>
       <c r="H15" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1741,16 +1741,16 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V15" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481075</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
@@ -1799,7 +1799,7 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O16" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
         <v>291.4220612627037</v>
@@ -1857,10 +1857,10 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H17" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
         <v>26.93768689770263</v>
@@ -1930,7 +1930,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>192.2280582198498</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
@@ -1939,7 +1939,7 @@
         <v>4.021973978873973</v>
       </c>
       <c r="I18" t="n">
-        <v>173.5918158819732</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S18" t="n">
         <v>131.8202263797057</v>
@@ -1975,16 +1975,16 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V18" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
         <v>78.39139276613435</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2048,7 +2048,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2091,13 +2091,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H20" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2158,22 +2158,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>213.6917283274922</v>
       </c>
       <c r="D21" t="n">
-        <v>121.9009546703283</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2200,25 +2200,25 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V21" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>419.8627394453875</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2276,16 +2276,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q22" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2331,10 +2331,10 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2398,13 +2398,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>195.2639131038855</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>3.99961134672543</v>
@@ -2449,10 +2449,10 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
         <v>111.3731429098285</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2522,7 +2522,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S25" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>343.0408141342571</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>21.67209722191262</v>
@@ -2644,13 +2644,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H27" t="n">
-        <v>4.021973978873961</v>
+        <v>177.6137898608471</v>
       </c>
       <c r="I27" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2686,10 +2686,10 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V27" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
         <v>111.3731429098285</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M28" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N28" t="n">
         <v>155.2579933044718</v>
@@ -2805,10 +2805,10 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
         <v>26.93768689770263</v>
@@ -2881,7 +2881,7 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>177.5914272286986</v>
+        <v>177.5914272286985</v>
       </c>
       <c r="H30" t="n">
         <v>4.021973978873961</v>
@@ -2920,13 +2920,13 @@
         <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
         <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W30" t="n">
         <v>111.3731429098285</v>
@@ -2993,10 +2993,10 @@
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598396</v>
+        <v>376.8716854102422</v>
       </c>
       <c r="S31" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         <v>89.33915573984979</v>
       </c>
       <c r="E32" t="n">
-        <v>83.82387697218276</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F32" t="n">
         <v>83.88962870801186</v>
@@ -3081,7 +3081,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U32" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3106,16 +3106,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>195.2639131038858</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>3.999611346725456</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>180.333570877285</v>
@@ -3160,7 +3160,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>174.1249482875295</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
@@ -3169,7 +3169,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>78.39139276613435</v>
@@ -3215,7 +3215,7 @@
         <v>10.3217920922054</v>
       </c>
       <c r="M34" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N34" t="n">
         <v>155.2579933044718</v>
@@ -3233,7 +3233,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S34" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3279,10 +3279,10 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3349,16 +3349,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>3.999611346725456</v>
       </c>
       <c r="H36" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
         <v>131.8202263797056</v>
       </c>
       <c r="T36" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
         <v>79.16168051490372</v>
@@ -3403,13 +3403,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>284.9649587918016</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481073</v>
       </c>
     </row>
     <row r="37">
@@ -3464,10 +3464,10 @@
         <v>291.4220612627037</v>
       </c>
       <c r="Q37" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R37" t="n">
-        <v>376.8716854102422</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
         <v>30.56285675203577</v>
@@ -3577,16 +3577,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C39" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>18.63624233787687</v>
@@ -3598,7 +3598,7 @@
         <v>4.021973978873961</v>
       </c>
       <c r="I39" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>483.2744725660229</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
         <v>131.8202263797056</v>
@@ -3634,7 +3634,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V39" t="n">
         <v>93.51066719152016</v>
@@ -3643,7 +3643,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
         <v>78.39139276613435</v>
@@ -3829,10 +3829,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873961</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>180.333570877285</v>
+        <v>353.9253867592579</v>
       </c>
       <c r="S42" t="n">
         <v>131.8202263797056</v>
@@ -3871,16 +3871,16 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>272.4545553273606</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>78.39139276613435</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3944,7 +3944,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,13 +3987,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4060,19 +4060,19 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>94.96326777262583</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,22 +4096,22 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>501.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V45" t="n">
-        <v>267.1024830734938</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
         <v>111.3731429098285</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M46" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N46" t="n">
         <v>155.2579933044718</v>
@@ -4172,13 +4172,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S46" t="n">
         <v>30.56285675203577</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.8416377852028</v>
+        <v>106.7884999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>54.86731632763319</v>
+        <v>56.81417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>44.42372467121926</v>
+        <v>46.37058683203599</v>
       </c>
       <c r="E2" t="n">
-        <v>40.016361431958</v>
+        <v>41.96322359277473</v>
       </c>
       <c r="F2" t="n">
-        <v>35.07734253497633</v>
+        <v>37.02420469579306</v>
       </c>
       <c r="G2" t="n">
         <v>33.64713203391685</v>
@@ -4324,22 +4324,22 @@
         <v>399.11</v>
       </c>
       <c r="K2" t="n">
-        <v>768.3799999999999</v>
+        <v>688.7700270351759</v>
       </c>
       <c r="L2" t="n">
-        <v>1137.65</v>
+        <v>753.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1433.335793611129</v>
+        <v>753.46</v>
       </c>
       <c r="N2" t="n">
-        <v>1433.335793611129</v>
+        <v>753.46</v>
       </c>
       <c r="O2" t="n">
-        <v>1433.335793611129</v>
+        <v>753.46</v>
       </c>
       <c r="P2" t="n">
-        <v>1492</v>
+        <v>1122.73</v>
       </c>
       <c r="Q2" t="n">
         <v>1492</v>
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1075.663263689516</v>
+        <v>375.9734315372855</v>
       </c>
       <c r="C3" t="n">
-        <v>913.3276633795579</v>
+        <v>375.9734315372855</v>
       </c>
       <c r="D3" t="n">
-        <v>913.3276633795579</v>
+        <v>375.9734315372855</v>
       </c>
       <c r="E3" t="n">
-        <v>913.3276633795579</v>
+        <v>29.84</v>
       </c>
       <c r="F3" t="n">
-        <v>570.2607519271569</v>
+        <v>29.84</v>
       </c>
       <c r="G3" t="n">
-        <v>241.454702729969</v>
+        <v>29.84</v>
       </c>
       <c r="H3" t="n">
-        <v>241.454702729969</v>
+        <v>29.84</v>
       </c>
       <c r="I3" t="n">
         <v>29.84</v>
       </c>
       <c r="J3" t="n">
-        <v>170.7984703728012</v>
+        <v>170.7984703728021</v>
       </c>
       <c r="K3" t="n">
-        <v>395.4085458068072</v>
+        <v>395.4085458068081</v>
       </c>
       <c r="L3" t="n">
-        <v>714.3818833454036</v>
+        <v>714.3818833454045</v>
       </c>
       <c r="M3" t="n">
-        <v>856.0360750882628</v>
+        <v>856.0360750882637</v>
       </c>
       <c r="N3" t="n">
         <v>1046.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1337.587921002191</v>
+        <v>1337.587921002192</v>
       </c>
       <c r="P3" t="n">
-        <v>1492</v>
+        <v>1492.000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>1345.738421006376</v>
+        <v>1345.738421006377</v>
       </c>
       <c r="R3" t="n">
-        <v>1210.871311105555</v>
+        <v>1197.127304098119</v>
       </c>
       <c r="S3" t="n">
-        <v>1147.791656100326</v>
+        <v>820.359627330442</v>
       </c>
       <c r="T3" t="n">
-        <v>1143.281782714996</v>
+        <v>443.5919505627651</v>
       </c>
       <c r="U3" t="n">
-        <v>1143.084020807432</v>
+        <v>443.3941886552008</v>
       </c>
       <c r="V3" t="n">
-        <v>1128.426781220038</v>
+        <v>428.7369490678067</v>
       </c>
       <c r="W3" t="n">
-        <v>1095.726636866676</v>
+        <v>396.0368047144446</v>
       </c>
       <c r="X3" t="n">
-        <v>1075.663263689516</v>
+        <v>375.9734315372855</v>
       </c>
       <c r="Y3" t="n">
-        <v>1075.663263689516</v>
+        <v>375.9734315372855</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>386.307098339975</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="C4" t="n">
-        <v>386.307098339975</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="D4" t="n">
-        <v>386.307098339975</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="E4" t="n">
-        <v>504.1360025513881</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="F4" t="n">
-        <v>504.1360025513881</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="G4" t="n">
-        <v>657.7264487661422</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="H4" t="n">
-        <v>657.7264487661422</v>
+        <v>676.8688082801704</v>
       </c>
       <c r="I4" t="n">
-        <v>884.3891106530448</v>
+        <v>903.5314701670729</v>
       </c>
       <c r="J4" t="n">
         <v>1253.659110653045</v>
@@ -4506,25 +4506,25 @@
         <v>29.84</v>
       </c>
       <c r="S4" t="n">
-        <v>29.84</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="T4" t="n">
-        <v>29.84</v>
+        <v>259.1561373677321</v>
       </c>
       <c r="U4" t="n">
-        <v>274.5497606736829</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="V4" t="n">
-        <v>274.5497606736829</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="W4" t="n">
-        <v>274.5497606736829</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="X4" t="n">
-        <v>274.5497606736829</v>
+        <v>505.7173598420843</v>
       </c>
       <c r="Y4" t="n">
-        <v>274.5497606736829</v>
+        <v>505.7173598420843</v>
       </c>
     </row>
     <row r="5">
@@ -4537,19 +4537,19 @@
         <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>56.89417848844987</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D5" t="n">
-        <v>46.45058683203594</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E5" t="n">
-        <v>42.04322359277468</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F5" t="n">
-        <v>37.10420469579301</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G5" t="n">
-        <v>33.72713203391683</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4558,25 +4558,25 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>30.01969029977264</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>400.2796902997726</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>770.5396902997726</v>
+        <v>1125.74</v>
       </c>
       <c r="M5" t="n">
-        <v>770.5396902997726</v>
+        <v>1125.74</v>
       </c>
       <c r="N5" t="n">
-        <v>1140.799690299772</v>
+        <v>1125.74</v>
       </c>
       <c r="O5" t="n">
-        <v>1140.799690299772</v>
+        <v>1125.74</v>
       </c>
       <c r="P5" t="n">
-        <v>1199.463896688644</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,10 +4585,10 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.724707412506</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.994415731961</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
         <v>969.3160547407873</v>
@@ -4603,7 +4603,7 @@
         <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.6960887900341</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>701.7929606495888</v>
+        <v>241.534702729969</v>
       </c>
       <c r="C6" t="n">
-        <v>701.7929606495888</v>
+        <v>241.534702729969</v>
       </c>
       <c r="D6" t="n">
-        <v>701.7929606495888</v>
+        <v>241.534702729969</v>
       </c>
       <c r="E6" t="n">
-        <v>701.7929606495888</v>
+        <v>241.534702729969</v>
       </c>
       <c r="F6" t="n">
-        <v>358.7260491971879</v>
+        <v>241.534702729969</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4664,25 +4664,25 @@
         <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1297.853320462484</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T6" t="n">
-        <v>1293.343447077155</v>
+        <v>920.0755426847068</v>
       </c>
       <c r="U6" t="n">
-        <v>1293.145685169591</v>
+        <v>542.2977649069289</v>
       </c>
       <c r="V6" t="n">
-        <v>1099.634111604526</v>
+        <v>294.2982202604903</v>
       </c>
       <c r="W6" t="n">
-        <v>721.856333826748</v>
+        <v>261.5980759071281</v>
       </c>
       <c r="X6" t="n">
-        <v>701.7929606495888</v>
+        <v>241.534702729969</v>
       </c>
       <c r="Y6" t="n">
-        <v>701.7929606495888</v>
+        <v>241.534702729969</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>686.8073391968559</v>
+        <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>686.8073391968559</v>
+        <v>29.92</v>
       </c>
       <c r="D7" t="n">
-        <v>686.8073391968559</v>
+        <v>143.2391441250001</v>
       </c>
       <c r="E7" t="n">
-        <v>804.6362434082689</v>
+        <v>261.0680483364131</v>
       </c>
       <c r="F7" t="n">
-        <v>928.9972160002044</v>
+        <v>385.4290209283486</v>
       </c>
       <c r="G7" t="n">
-        <v>1082.587662214959</v>
+        <v>481.6391623681918</v>
       </c>
       <c r="H7" t="n">
-        <v>1253.739110653045</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="I7" t="n">
-        <v>1253.739110653045</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="J7" t="n">
-        <v>1253.739110653045</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K7" t="n">
-        <v>1385.467095409585</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
         <v>1385.467095409585</v>
@@ -4749,19 +4749,19 @@
         <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>276.4812224743522</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>475.3026153602981</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>647.1935336199756</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>647.1935336199756</v>
+        <v>29.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>686.8073391968559</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.8684999460195</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>56.89417848844987</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>46.45058683203594</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>42.04322359277468</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>37.10420469579301</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>33.72713203391683</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>400.18</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K8" t="n">
-        <v>770.4399999999999</v>
+        <v>326.5557936111288</v>
       </c>
       <c r="L8" t="n">
-        <v>1140.7</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="M8" t="n">
-        <v>1140.7</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N8" t="n">
-        <v>1140.7</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1140.7</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
-        <v>1199.364206388871</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1494.026862160817</v>
+        <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.751569573322</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.021277892777</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3160547407873</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1433030571268</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>496.3620141874828</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1379399847881</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.6960887900341</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>372.9869114524009</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="C9" t="n">
-        <v>372.9869114524009</v>
+        <v>860.9775417430701</v>
       </c>
       <c r="D9" t="n">
-        <v>372.9869114524009</v>
+        <v>860.9775417430701</v>
       </c>
       <c r="E9" t="n">
-        <v>372.9869114524009</v>
+        <v>514.8441102057845</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>171.7771987533836</v>
       </c>
       <c r="G9" t="n">
         <v>29.92</v>
@@ -4898,28 +4898,28 @@
         <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1118.022307590758</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>822.8930816409878</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>818.3832082556585</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>818.1854463480942</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V9" t="n">
-        <v>803.5282067607001</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W9" t="n">
-        <v>770.8280624073379</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X9" t="n">
-        <v>750.7646892301788</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="Y9" t="n">
-        <v>750.7646892301788</v>
+        <v>1225.724928051676</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>568.6335335607477</v>
+        <v>950.0884130403253</v>
       </c>
       <c r="C10" t="n">
-        <v>568.6335335607477</v>
+        <v>950.0884130403253</v>
       </c>
       <c r="D10" t="n">
-        <v>681.9526776857477</v>
+        <v>950.0884130403253</v>
       </c>
       <c r="E10" t="n">
-        <v>681.9526776857477</v>
+        <v>950.0884130403253</v>
       </c>
       <c r="F10" t="n">
-        <v>681.9526776857477</v>
+        <v>950.0884130403253</v>
       </c>
       <c r="G10" t="n">
-        <v>835.5431239005019</v>
+        <v>950.0884130403253</v>
       </c>
       <c r="H10" t="n">
-        <v>1006.694572338588</v>
+        <v>950.0884130403253</v>
       </c>
       <c r="I10" t="n">
-        <v>1006.694572338588</v>
+        <v>950.0884130403253</v>
       </c>
       <c r="J10" t="n">
-        <v>1253.739110653045</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K10" t="n">
-        <v>1385.467095409585</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L10" t="n">
         <v>1385.467095409585</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7813496506081</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="U10" t="n">
-        <v>218.7813496506081</v>
+        <v>316.9360101914762</v>
       </c>
       <c r="V10" t="n">
-        <v>417.6027425365541</v>
+        <v>515.7574030774222</v>
       </c>
       <c r="W10" t="n">
-        <v>417.6027425365541</v>
+        <v>687.6483213370996</v>
       </c>
       <c r="X10" t="n">
-        <v>568.6335335607477</v>
+        <v>838.6791123612931</v>
       </c>
       <c r="Y10" t="n">
-        <v>568.6335335607477</v>
+        <v>950.0884130403253</v>
       </c>
     </row>
     <row r="11">
@@ -5008,49 +5008,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D11" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E11" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F11" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G11" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H11" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>733.5813277110226</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L11" t="n">
-        <v>949.6332762537361</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M11" t="n">
-        <v>949.6332762537362</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N11" t="n">
-        <v>1592.143276253736</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
-        <v>1753.273377636691</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P11" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
@@ -5065,19 +5065,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W11" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X11" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>492.6952769985968</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C12" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424893</v>
       </c>
       <c r="D12" t="n">
-        <v>100.7381059448373</v>
+        <v>924.5682229973352</v>
       </c>
       <c r="E12" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600496</v>
       </c>
       <c r="F12" t="n">
-        <v>60.0226114399994</v>
+        <v>559.610304250073</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463099</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5138,25 +5138,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S12" t="n">
-        <v>1753.535205884733</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T12" t="n">
-        <v>1671.337882527992</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U12" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V12" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W12" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X12" t="n">
-        <v>1284.561892566739</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y12" t="n">
-        <v>881.1362433080176</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="13">
@@ -5196,19 +5196,19 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
         <v>464.3167555675508</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C14" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D14" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E14" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F14" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G14" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H14" t="n">
         <v>51.92</v>
@@ -5269,25 +5269,25 @@
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L14" t="n">
-        <v>1418.446838088717</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M14" t="n">
-        <v>1418.446838088717</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N14" t="n">
-        <v>1418.446838088717</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O14" t="n">
-        <v>2060.956838088718</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5296,25 +5296,25 @@
         <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U14" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X14" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="15">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>992.2829698086708</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C15" t="n">
-        <v>627.5355835000655</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D15" t="n">
-        <v>424.9805301872616</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E15" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F15" t="n">
-        <v>384.2650356824237</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G15" t="n">
-        <v>380.2250242210849</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5384,16 +5384,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V15" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W15" t="n">
-        <v>1235.526089867104</v>
+        <v>911.2836656246793</v>
       </c>
       <c r="X15" t="n">
-        <v>1135.664736891965</v>
+        <v>487.1798884071161</v>
       </c>
       <c r="Y15" t="n">
-        <v>1056.481511875667</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="16">
@@ -5433,13 +5433,13 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L16" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M16" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N16" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O16" t="n">
         <v>1115.142339091088</v>
@@ -5500,31 +5500,31 @@
         <v>125.9679517166617</v>
       </c>
       <c r="H17" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>307.5796384907274</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L17" t="n">
-        <v>523.631587033441</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="M17" t="n">
-        <v>1166.141587033441</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="N17" t="n">
-        <v>1808.651587033441</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O17" t="n">
-        <v>1969.781688416396</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P17" t="n">
-        <v>2166.373694755016</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>668.0405455662465</v>
+        <v>668.0405455662462</v>
       </c>
       <c r="C18" t="n">
-        <v>627.5355835000654</v>
+        <v>303.2931592576409</v>
       </c>
       <c r="D18" t="n">
-        <v>600.3257987549113</v>
+        <v>276.0833745124867</v>
       </c>
       <c r="E18" t="n">
-        <v>578.4347914600501</v>
+        <v>254.1923672176254</v>
       </c>
       <c r="F18" t="n">
-        <v>235.3678800076491</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G18" t="n">
-        <v>231.3278685463103</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H18" t="n">
-        <v>227.2652685676497</v>
+        <v>51.92</v>
       </c>
       <c r="I18" t="n">
         <v>51.92</v>
@@ -5609,13 +5609,13 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R18" t="n">
-        <v>1737.789794027844</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S18" t="n">
-        <v>1604.638050209959</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T18" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U18" t="n">
         <v>1442.479433403819</v>
@@ -5624,13 +5624,13 @@
         <v>1348.024214018445</v>
       </c>
       <c r="W18" t="n">
-        <v>1235.526089867104</v>
+        <v>911.2836656246791</v>
       </c>
       <c r="X18" t="n">
-        <v>811.4223126495403</v>
+        <v>811.4223126495401</v>
       </c>
       <c r="Y18" t="n">
-        <v>732.239087633243</v>
+        <v>732.2390876332428</v>
       </c>
     </row>
     <row r="19">
@@ -5670,25 +5670,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M19" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N19" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O19" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C20" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D20" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E20" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F20" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G20" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H20" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
@@ -5746,7 +5746,7 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>737.2059437357115</v>
+        <v>310.7478922784251</v>
       </c>
       <c r="L20" t="n">
         <v>953.2578922784251</v>
@@ -5779,16 +5779,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W20" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>912.8601939406431</v>
+        <v>343.7981213238219</v>
       </c>
       <c r="C21" t="n">
-        <v>548.1128076320376</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D21" t="n">
-        <v>424.9805301872615</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E21" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F21" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5843,31 +5843,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R21" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S21" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T21" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U21" t="n">
-        <v>1687.299081778216</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V21" t="n">
-        <v>1592.843862392842</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W21" t="n">
-        <v>1480.3457382415</v>
+        <v>911.2836656246791</v>
       </c>
       <c r="X21" t="n">
-        <v>1056.241961023937</v>
+        <v>487.1798884071159</v>
       </c>
       <c r="Y21" t="n">
-        <v>977.0587360076396</v>
+        <v>407.9966633908185</v>
       </c>
     </row>
     <row r="22">
@@ -5919,13 +5919,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5974,31 +5974,31 @@
         <v>125.9679517166617</v>
       </c>
       <c r="H23" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K23" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L23" t="n">
-        <v>523.631587033441</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M23" t="n">
-        <v>1166.141587033441</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N23" t="n">
-        <v>1651.83297330616</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="O23" t="n">
-        <v>1812.963074689115</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="P23" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>668.0405455662462</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C24" t="n">
-        <v>303.2931592576409</v>
+        <v>951.7780077424893</v>
       </c>
       <c r="D24" t="n">
-        <v>276.0833745124867</v>
+        <v>600.3257987549109</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F24" t="n">
         <v>60.0226114399994</v>
@@ -6092,19 +6092,19 @@
         <v>1846.683151095641</v>
       </c>
       <c r="U24" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V24" t="n">
-        <v>1023.781789776021</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>911.2836656246791</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>811.4223126495401</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>732.2390876332428</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="25">
@@ -6144,25 +6144,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L25" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M25" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N25" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O25" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q25" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R25" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6220,16 +6220,16 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K26" t="n">
-        <v>1201.938527309012</v>
+        <v>898.3360451186668</v>
       </c>
       <c r="L26" t="n">
-        <v>1844.448527309012</v>
+        <v>1114.38799366138</v>
       </c>
       <c r="M26" t="n">
-        <v>1844.448527309012</v>
+        <v>1114.38799366138</v>
       </c>
       <c r="N26" t="n">
-        <v>1844.448527309012</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="O26" t="n">
         <v>2399.40799366138</v>
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>668.0405455662465</v>
+        <v>992.2829698086707</v>
       </c>
       <c r="C27" t="n">
-        <v>321.5346727033605</v>
+        <v>951.7780077424896</v>
       </c>
       <c r="D27" t="n">
-        <v>294.3248879582063</v>
+        <v>600.3257987549111</v>
       </c>
       <c r="E27" t="n">
-        <v>272.4338806633451</v>
+        <v>578.43479146005</v>
       </c>
       <c r="F27" t="n">
-        <v>253.6093934533685</v>
+        <v>559.6103042500733</v>
       </c>
       <c r="G27" t="n">
-        <v>249.5693819920296</v>
+        <v>231.3278685463102</v>
       </c>
       <c r="H27" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6329,19 +6329,19 @@
         <v>1846.683151095642</v>
       </c>
       <c r="U27" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V27" t="n">
-        <v>1023.781789776021</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W27" t="n">
-        <v>911.2836656246793</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X27" t="n">
-        <v>811.4223126495403</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y27" t="n">
-        <v>732.239087633243</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="28">
@@ -6381,7 +6381,7 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M28" t="n">
         <v>1506.07469544798</v>
@@ -6448,28 +6448,28 @@
         <v>125.9679517166614</v>
       </c>
       <c r="H29" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>1201.938527309012</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L29" t="n">
-        <v>1844.448527309012</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M29" t="n">
-        <v>1844.448527309012</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N29" t="n">
-        <v>1844.448527309012</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O29" t="n">
-        <v>2005.578628691967</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P29" t="n">
         <v>2596</v>
@@ -6509,19 +6509,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>668.0405455662465</v>
+        <v>992.2829698086707</v>
       </c>
       <c r="C30" t="n">
-        <v>627.5355835000654</v>
+        <v>627.5355835000653</v>
       </c>
       <c r="D30" t="n">
-        <v>600.3257987549113</v>
+        <v>600.3257987549111</v>
       </c>
       <c r="E30" t="n">
-        <v>254.1923672176258</v>
+        <v>254.1923672176256</v>
       </c>
       <c r="F30" t="n">
-        <v>235.3678800076491</v>
+        <v>235.367880007649</v>
       </c>
       <c r="G30" t="n">
         <v>55.98259997866057</v>
@@ -6563,22 +6563,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U30" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1023.781789776021</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W30" t="n">
-        <v>911.2836656246793</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X30" t="n">
-        <v>811.4223126495403</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y30" t="n">
-        <v>732.239087633243</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="31">
@@ -6636,7 +6636,7 @@
         <v>463.4700425881596</v>
       </c>
       <c r="R31" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S31" t="n">
         <v>51.92</v>
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D32" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E32" t="n">
         <v>292.4361325821661</v>
@@ -6694,13 +6694,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K32" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L32" t="n">
-        <v>523.631587033441</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M32" t="n">
-        <v>1166.141587033441</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N32" t="n">
         <v>1651.83297330616</v>
@@ -6724,19 +6724,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="33">
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>816.9377012410212</v>
+        <v>668.0405455662465</v>
       </c>
       <c r="C33" t="n">
-        <v>452.1903149324157</v>
+        <v>627.5355835000654</v>
       </c>
       <c r="D33" t="n">
-        <v>424.9805301872615</v>
+        <v>600.3257987549113</v>
       </c>
       <c r="E33" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F33" t="n">
         <v>60.02261143999941</v>
@@ -6791,31 +6791,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q33" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R33" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S33" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T33" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U33" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V33" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W33" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X33" t="n">
-        <v>1284.561892566739</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y33" t="n">
-        <v>1205.378667550442</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="34">
@@ -6858,22 +6858,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M34" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N34" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O34" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P34" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R34" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6922,7 +6922,7 @@
         <v>125.9679517166614</v>
       </c>
       <c r="H35" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
@@ -6934,19 +6934,19 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L35" t="n">
-        <v>1418.446838088717</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M35" t="n">
-        <v>1418.446838088717</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N35" t="n">
-        <v>1756.89799366138</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O35" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P35" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>816.9377012410212</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C36" t="n">
-        <v>452.1903149324158</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D36" t="n">
-        <v>424.9805301872616</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E36" t="n">
         <v>403.0895228924003</v>
       </c>
       <c r="F36" t="n">
-        <v>384.2650356824237</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G36" t="n">
-        <v>380.2250242210849</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7037,22 +7037,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U36" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V36" t="n">
-        <v>1348.024214018445</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W36" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>960.319468324315</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y36" t="n">
-        <v>881.1362433080177</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="37">
@@ -7107,7 +7107,7 @@
         <v>819.9299076645212</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R37" t="n">
         <v>82.79157247680381</v>
@@ -7165,22 +7165,22 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L38" t="n">
-        <v>523.631587033441</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M38" t="n">
-        <v>1166.141587033441</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N38" t="n">
-        <v>1310.98</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O38" t="n">
-        <v>1953.49</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P38" t="n">
         <v>2596</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>362.0396347695416</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C39" t="n">
-        <v>321.5346727033605</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D39" t="n">
-        <v>294.3248879582063</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E39" t="n">
-        <v>272.4338806633451</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F39" t="n">
-        <v>253.6093934533685</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G39" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H39" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I39" t="n">
         <v>51.92</v>
@@ -7268,28 +7268,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R39" t="n">
-        <v>1756.031307473563</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S39" t="n">
-        <v>1622.879563655678</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T39" t="n">
-        <v>1540.682240298937</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U39" t="n">
-        <v>1136.478522607115</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V39" t="n">
-        <v>1042.023303221741</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>929.5251790703987</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X39" t="n">
-        <v>505.4214018528356</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y39" t="n">
-        <v>426.2381768365382</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="40">
@@ -7402,25 +7402,25 @@
         <v>51.92</v>
       </c>
       <c r="J41" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K41" t="n">
-        <v>775.9368380887173</v>
+        <v>953.2578922784252</v>
       </c>
       <c r="L41" t="n">
-        <v>1009.32297330616</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="M41" t="n">
-        <v>1009.32297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="N41" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O41" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P41" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>492.6952769985969</v>
+        <v>1141.180125483446</v>
       </c>
       <c r="C42" t="n">
-        <v>452.1903149324158</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D42" t="n">
-        <v>424.9805301872616</v>
+        <v>1073.46537867211</v>
       </c>
       <c r="E42" t="n">
-        <v>403.0895228924003</v>
+        <v>1051.574371377249</v>
       </c>
       <c r="F42" t="n">
-        <v>60.02261143999941</v>
+        <v>708.507459924848</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866057</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H42" t="n">
         <v>51.92</v>
@@ -7505,28 +7505,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>2062.032218270268</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S42" t="n">
-        <v>1928.880474452383</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095642</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U42" t="n">
-        <v>1442.479433403819</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V42" t="n">
-        <v>1348.024214018445</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W42" t="n">
-        <v>911.2836656246793</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X42" t="n">
-        <v>636.0770440818908</v>
+        <v>1284.56189256674</v>
       </c>
       <c r="Y42" t="n">
-        <v>556.8938190655934</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="43">
@@ -7566,25 +7566,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L43" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N43" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O43" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q43" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R43" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7615,43 +7615,43 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C44" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D44" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E44" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F44" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G44" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H44" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I44" t="n">
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>137.738325744391</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K44" t="n">
-        <v>311.8911261464011</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L44" t="n">
-        <v>527.9430746891146</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M44" t="n">
-        <v>1170.453074689115</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N44" t="n">
-        <v>1170.453074689115</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O44" t="n">
         <v>1812.963074689115</v>
@@ -7675,16 +7675,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W44" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X44" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>816.937701241021</v>
+        <v>264.3753454557946</v>
       </c>
       <c r="C45" t="n">
-        <v>776.43273917484</v>
+        <v>223.8703833896135</v>
       </c>
       <c r="D45" t="n">
-        <v>749.2229544296858</v>
+        <v>196.6605986444593</v>
       </c>
       <c r="E45" t="n">
-        <v>403.0895228924003</v>
+        <v>174.7695913495981</v>
       </c>
       <c r="F45" t="n">
-        <v>384.2650356824237</v>
+        <v>155.9451041396215</v>
       </c>
       <c r="G45" t="n">
-        <v>380.2250242210849</v>
+        <v>151.9050926782826</v>
       </c>
       <c r="H45" t="n">
-        <v>51.92</v>
+        <v>147.8424926996221</v>
       </c>
       <c r="I45" t="n">
         <v>51.92</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R45" t="n">
-        <v>1737.789794027844</v>
+        <v>1658.367018159816</v>
       </c>
       <c r="S45" t="n">
-        <v>1604.638050209959</v>
+        <v>1200.972850099507</v>
       </c>
       <c r="T45" t="n">
-        <v>1522.440726853217</v>
+        <v>1118.775526742765</v>
       </c>
       <c r="U45" t="n">
-        <v>1442.47943340382</v>
+        <v>714.5718090509433</v>
       </c>
       <c r="V45" t="n">
-        <v>1172.678945450796</v>
+        <v>620.1165896655694</v>
       </c>
       <c r="W45" t="n">
-        <v>1060.180821299454</v>
+        <v>507.6184655142275</v>
       </c>
       <c r="X45" t="n">
-        <v>960.3194683243149</v>
+        <v>407.7571125390886</v>
       </c>
       <c r="Y45" t="n">
-        <v>881.1362433080176</v>
+        <v>328.5738875227912</v>
       </c>
     </row>
     <row r="46">
@@ -7806,19 +7806,19 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M46" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N46" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O46" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
         <v>820.7766206439126</v>
       </c>
       <c r="Q46" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R46" t="n">
         <v>82.79157247680381</v>
@@ -7967,13 +7967,13 @@
         <v>372.8993027275024</v>
       </c>
       <c r="K2" t="n">
-        <v>320.3286984924623</v>
+        <v>239.9145843865794</v>
       </c>
       <c r="L2" t="n">
-        <v>307.6565929648241</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>770.2275157881712</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N2" t="n">
         <v>403.3653500296342</v>
@@ -7982,10 +7982,10 @@
         <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>313.7432258698271</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.1077446289929</v>
+        <v>501.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8043,7 +8043,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>223.7070799393687</v>
+        <v>223.7070799393696</v>
       </c>
       <c r="K3" t="n">
         <v>295.8802408630135</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K5" t="n">
         <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
-        <v>308.6565929648241</v>
+        <v>293.545481853713</v>
       </c>
       <c r="M5" t="n">
         <v>471.5549969890509</v>
       </c>
       <c r="N5" t="n">
-        <v>777.3653500296342</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
         <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>314.7432258698271</v>
       </c>
       <c r="Q5" t="n">
-        <v>427.6391621152114</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,16 +8438,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>373.8993027275024</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321.3286984924623</v>
+        <v>246.8601159786807</v>
       </c>
       <c r="L8" t="n">
         <v>308.6565929648241</v>
       </c>
       <c r="M8" t="n">
-        <v>471.5549969890509</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
         <v>403.3653500296342</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>427.7398593877089</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,16 +8675,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
         <v>879.4920535472222</v>
@@ -8693,10 +8693,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>60.29262328527639</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>430.7657085427136</v>
+        <v>60.29262328527625</v>
       </c>
       <c r="M14" t="n">
         <v>301.434429149855</v>
       </c>
       <c r="N14" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O14" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>341.8698541138006</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>179.5731479057567</v>
       </c>
       <c r="M17" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>457.4494331410071</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,10 +9389,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>433.9659648939233</v>
+        <v>3.200256351209731</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M20" t="n">
         <v>950.4344291498551</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9635,16 +9635,16 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>721.0894134186553</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>166.4189064723675</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,19 +9863,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>473.08808040201</v>
+        <v>166.4189064723679</v>
       </c>
       <c r="L26" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>301.434429149855</v>
       </c>
       <c r="N26" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
-        <v>397.8074393630433</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -10097,25 +10097,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L29" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M29" t="n">
-        <v>301.434429149855</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N29" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>397.8074393630432</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>23.48346824708341</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M32" t="n">
-        <v>950.4344291498551</v>
+        <v>537.1780000765643</v>
       </c>
       <c r="N32" t="n">
-        <v>721.0894134186553</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10577,22 +10577,22 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L35" t="n">
-        <v>430.7657085427136</v>
+        <v>17.50927946942295</v>
       </c>
       <c r="M35" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>572.361907661023</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O35" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,25 +10808,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.661228307766578</v>
       </c>
       <c r="M38" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N38" t="n">
-        <v>376.7934807861708</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O38" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>23.48346824708341</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>473.0880804020101</v>
+        <v>221.8955197650531</v>
       </c>
       <c r="L41" t="n">
-        <v>17.50927946942295</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M41" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,22 +11282,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>4.355038036033974</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>60.29262328527625</v>
       </c>
       <c r="M44" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N44" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O44" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.927393539208538</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.927393539208561</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23426,7 +23426,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23657,7 +23657,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,10 +24596,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -24851,10 +24851,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25073,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25322,10 +25322,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="R37" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -25781,7 +25781,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26021,7 +26021,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -26030,7 +26030,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -26296,13 +26296,13 @@
         <v>1290840.845493009</v>
       </c>
       <c r="K2" t="n">
-        <v>1290840.84549301</v>
+        <v>1290840.845493009</v>
       </c>
       <c r="L2" t="n">
         <v>1290840.84549301</v>
       </c>
       <c r="M2" t="n">
-        <v>1290840.845493009</v>
+        <v>1290840.84549301</v>
       </c>
       <c r="N2" t="n">
         <v>1290840.84549301</v>
@@ -26311,7 +26311,7 @@
         <v>1290840.84549301</v>
       </c>
       <c r="P2" t="n">
-        <v>1290840.845493009</v>
+        <v>1290840.84549301</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577307.7597977305</v>
+        <v>570823.1065049332</v>
       </c>
       <c r="C4" t="n">
-        <v>575232.1895180241</v>
+        <v>568738.1032495913</v>
       </c>
       <c r="D4" t="n">
-        <v>573221.1009892204</v>
+        <v>566727.0147207878</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259448</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216768</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286013</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604934</v>
+        <v>466508.6099301391</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>423124.0505043155</v>
+        <v>429608.7037971128</v>
       </c>
       <c r="C6" t="n">
-        <v>656665.0768228859</v>
+        <v>663159.1630913187</v>
       </c>
       <c r="D6" t="n">
-        <v>659028.1653516896</v>
+        <v>665522.251620122</v>
       </c>
       <c r="E6" t="n">
-        <v>138382.3166968353</v>
+        <v>144845.3078271893</v>
       </c>
       <c r="F6" t="n">
-        <v>728643.3795150574</v>
+        <v>735106.3706454119</v>
       </c>
       <c r="G6" t="n">
-        <v>730331.7690367111</v>
+        <v>736794.7601670652</v>
       </c>
       <c r="H6" t="n">
-        <v>732022.5019466731</v>
+        <v>738485.4930770281</v>
       </c>
       <c r="I6" t="n">
-        <v>733715.5951472211</v>
+        <v>740178.5862775753</v>
       </c>
       <c r="J6" t="n">
-        <v>347315.0657621446</v>
+        <v>353778.0568924991</v>
       </c>
       <c r="K6" t="n">
-        <v>736756.9311409788</v>
+        <v>743219.9222713326</v>
       </c>
       <c r="L6" t="n">
-        <v>738809.2088633227</v>
+        <v>745272.1999936767</v>
       </c>
       <c r="M6" t="n">
-        <v>643711.91674329</v>
+        <v>650174.9078736446</v>
       </c>
       <c r="N6" t="n">
-        <v>742217.072834054</v>
+        <v>748680.0639644082</v>
       </c>
       <c r="O6" t="n">
-        <v>487124.6954325164</v>
+        <v>493587.6865628705</v>
       </c>
       <c r="P6" t="n">
-        <v>745634.8030840994</v>
+        <v>752097.7942144539</v>
       </c>
     </row>
   </sheetData>
@@ -26975,19 +26975,19 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27515,25 +27515,25 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>200.3876681386602</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
         <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,13 +27560,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>386.3934330626371</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>89.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>31.46477465147608</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>272.7252466480447</v>
@@ -27600,22 +27600,22 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
+        <v>244.858135136612</v>
+      </c>
+      <c r="H4" t="n">
         <v>400</v>
-      </c>
-      <c r="H4" t="n">
-        <v>227.1197490524383</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>395.1372930982029</v>
+        <v>375.8015764173663</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2309599488807</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>398.1298365649805</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27721,13 +27721,13 @@
         <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
       </c>
       <c r="U5" t="n">
-        <v>398.0465935392084</v>
+        <v>400</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
@@ -27761,16 +27761,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
         <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27803,16 +27803,16 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
+        <v>30.46477465147608</v>
+      </c>
+      <c r="U6" t="n">
+        <v>26.19578428848864</v>
+      </c>
+      <c r="V6" t="n">
+        <v>168.9911179915459</v>
+      </c>
+      <c r="W6" t="n">
         <v>400</v>
-      </c>
-      <c r="U6" t="n">
-        <v>400</v>
-      </c>
-      <c r="V6" t="n">
-        <v>222.9342093621061</v>
-      </c>
-      <c r="W6" t="n">
-        <v>58.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27834,7 +27834,7 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -27843,22 +27843,22 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>342.0400961869587</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.047816275856</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.13729309820286</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27885,19 +27885,19 @@
         <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>327.4792978766142</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>222.9148456338345</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,22 +27986,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.517988705216</v>
+        <v>185.0793619393662</v>
       </c>
       <c r="H9" t="n">
         <v>330.0284079411381</v>
@@ -28034,10 +28034,10 @@
         <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>159.5184388018133</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>170.2709247649051</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28071,7 +28071,7 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
@@ -28080,22 +28080,22 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I10" t="n">
         <v>171.047816275856</v>
       </c>
       <c r="J10" t="n">
-        <v>271.6772307895733</v>
+        <v>324.7886664849252</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
+        <v>209.2309599488807</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
-      </c>
-      <c r="U10" t="n">
-        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28201,7 +28201,7 @@
         <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V11" t="n">
         <v>321</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -28232,16 +28232,16 @@
         <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>321</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="I12" t="n">
         <v>191.6509141932353</v>
@@ -28274,7 +28274,7 @@
         <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28292,7 +28292,7 @@
         <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28399,7 +28399,7 @@
         <v>321</v>
       </c>
       <c r="H14" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I14" t="n">
         <v>96.76634561233286</v>
@@ -28432,7 +28432,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S14" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T14" t="n">
         <v>321</v>
@@ -28463,10 +28463,10 @@
         <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
@@ -28478,7 +28478,7 @@
         <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I15" t="n">
         <v>191.6509141932353</v>
@@ -28520,16 +28520,16 @@
         <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
     </row>
     <row r="16">
@@ -28636,10 +28636,10 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I17" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28700,7 +28700,7 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>321</v>
@@ -28709,7 +28709,7 @@
         <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28718,7 +28718,7 @@
         <v>321</v>
       </c>
       <c r="I18" t="n">
-        <v>18.05909831126212</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28745,7 +28745,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S18" t="n">
         <v>321</v>
@@ -28754,16 +28754,16 @@
         <v>321</v>
       </c>
       <c r="U18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y18" t="n">
         <v>321</v>
@@ -28873,10 +28873,10 @@
         <v>321</v>
       </c>
       <c r="H20" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I20" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28937,13 +28937,13 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="D21" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
         <v>321</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R21" t="n">
         <v>321</v>
@@ -28991,13 +28991,13 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>321</v>
       </c>
       <c r="W21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -29110,10 +29110,10 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I23" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29177,13 +29177,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>147.4081841180271</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29228,10 +29228,10 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
         <v>321</v>
@@ -29408,13 +29408,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>18.05909831126223</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>321</v>
@@ -29423,13 +29423,13 @@
         <v>321</v>
       </c>
       <c r="G27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29465,10 +29465,10 @@
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W27" t="n">
         <v>321</v>
@@ -29584,10 +29584,10 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29645,10 +29645,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>321</v>
@@ -29660,7 +29660,7 @@
         <v>321</v>
       </c>
       <c r="G30" t="n">
-        <v>147.4081841180268</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="H30" t="n">
         <v>321</v>
@@ -29699,13 +29699,13 @@
         <v>321</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U30" t="n">
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W30" t="n">
         <v>321</v>
@@ -29812,7 +29812,7 @@
         <v>321</v>
       </c>
       <c r="E32" t="n">
-        <v>320.5394126346859</v>
+        <v>321</v>
       </c>
       <c r="F32" t="n">
         <v>321</v>
@@ -29860,7 +29860,7 @@
         <v>321</v>
       </c>
       <c r="U32" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V32" t="n">
         <v>321</v>
@@ -29885,16 +29885,16 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
         <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
         <v>321</v>
@@ -29939,7 +29939,7 @@
         <v>321</v>
       </c>
       <c r="U33" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="V33" t="n">
         <v>321</v>
@@ -29948,7 +29948,7 @@
         <v>321</v>
       </c>
       <c r="X33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>321</v>
@@ -30058,10 +30058,10 @@
         <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I35" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30128,16 +30128,16 @@
         <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I36" t="n">
         <v>191.6509141932353</v>
@@ -30173,7 +30173,7 @@
         <v>321</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U36" t="n">
         <v>321</v>
@@ -30182,13 +30182,13 @@
         <v>321</v>
       </c>
       <c r="W36" t="n">
+        <v>321</v>
+      </c>
+      <c r="X36" t="n">
+        <v>321</v>
+      </c>
+      <c r="Y36" t="n">
         <v>147.408184118027</v>
-      </c>
-      <c r="X36" t="n">
-        <v>321</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>321</v>
       </c>
     </row>
     <row r="37">
@@ -30356,16 +30356,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>321</v>
@@ -30377,7 +30377,7 @@
         <v>321</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30404,7 +30404,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
-        <v>18.05909831126201</v>
+        <v>321</v>
       </c>
       <c r="S39" t="n">
         <v>321</v>
@@ -30413,7 +30413,7 @@
         <v>321</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V39" t="n">
         <v>321</v>
@@ -30422,7 +30422,7 @@
         <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y39" t="n">
         <v>321</v>
@@ -30608,10 +30608,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>191.6509141932353</v>
@@ -30641,7 +30641,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="S42" t="n">
         <v>321</v>
@@ -30650,16 +30650,16 @@
         <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V42" t="n">
         <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="Y42" t="n">
         <v>321</v>
@@ -30769,10 +30769,10 @@
         <v>321</v>
       </c>
       <c r="H44" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I44" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30839,7 +30839,7 @@
         <v>321</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F45" t="n">
         <v>321</v>
@@ -30848,10 +30848,10 @@
         <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I45" t="n">
-        <v>191.6509141932353</v>
+        <v>96.6876464206095</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,22 +30875,22 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>147.4081841180264</v>
+        <v>321</v>
       </c>
       <c r="W45" t="n">
         <v>321</v>
@@ -34746,25 +34746,25 @@
         <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>372.9999999999999</v>
+        <v>292.5858858941171</v>
       </c>
       <c r="L2" t="n">
+        <v>65.34340703517591</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>373</v>
       </c>
-      <c r="M2" t="n">
-        <v>298.6725187991202</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>59.25677413017286</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,7 +34822,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>142.3822933058598</v>
+        <v>142.3822933058607</v>
       </c>
       <c r="K3" t="n">
         <v>226.8788640747536</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -34886,22 +34886,22 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
         <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>353.6642833191635</v>
       </c>
       <c r="K4" t="n">
         <v>133.058570461152</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>247.1815764380635</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1006972724976123</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
+        <v>373.9999999999999</v>
+      </c>
+      <c r="L5" t="n">
+        <v>358.8888888888889</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>374</v>
       </c>
-      <c r="L5" t="n">
-        <v>374</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>374</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>59.25677413017286</v>
-      </c>
       <c r="Q5" t="n">
-        <v>299.5314174862185</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35120,7 +35120,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
@@ -35129,22 +35129,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>155.141864863388</v>
+        <v>97.18196105034673</v>
       </c>
       <c r="H7" t="n">
         <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
         <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35171,19 +35171,19 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>40.0139450271518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35217,16 +35217,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>374</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K8" t="n">
-        <v>373.9999999999999</v>
+        <v>299.5314174862184</v>
       </c>
       <c r="L8" t="n">
         <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>299.6321147587159</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35357,7 +35357,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -35366,22 +35366,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>249.5399376913705</v>
+        <v>302.6513733867223</v>
       </c>
       <c r="K10" t="n">
         <v>133.058570461152</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,16 +35454,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L11" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N11" t="n">
         <v>649</v>
@@ -35472,10 +35472,10 @@
         <v>162.757678164601</v>
       </c>
       <c r="P11" t="n">
-        <v>258.8704074657005</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L14" t="n">
+        <v>278.5269147425627</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>649</v>
       </c>
-      <c r="L14" t="n">
-        <v>649</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
       <c r="O14" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P14" t="n">
-        <v>540.4476382942246</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>218.2342914572864</v>
+        <v>397.8074393630432</v>
       </c>
       <c r="M17" t="n">
         <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -35949,7 +35949,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>433.9659648939237</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,10 +36168,10 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>609.8778844919133</v>
+        <v>179.1121759491997</v>
       </c>
       <c r="L20" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M20" t="n">
         <v>649</v>
@@ -36317,7 +36317,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H22" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I22" t="n">
         <v>163.0214951995539</v>
@@ -36402,7 +36402,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K23" t="n">
         <v>175.9119195979899</v>
@@ -36414,16 +36414,16 @@
         <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>490.5973598714331</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>162.757678164601</v>
+        <v>649</v>
       </c>
       <c r="P23" t="n">
-        <v>198.5777841804241</v>
+        <v>364.9966906527916</v>
       </c>
       <c r="Q23" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36642,19 +36642,19 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K26" t="n">
-        <v>648.9999999999999</v>
+        <v>342.3308260703578</v>
       </c>
       <c r="L26" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>649</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
-        <v>560.5651175276442</v>
+        <v>649</v>
       </c>
       <c r="P26" t="n">
         <v>198.5777841804241</v>
@@ -36876,25 +36876,25 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L29" t="n">
         <v>649</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P29" t="n">
-        <v>596.3852235434673</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -37116,16 +37116,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K32" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L32" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M32" t="n">
-        <v>649</v>
+        <v>235.7435709267093</v>
       </c>
       <c r="N32" t="n">
-        <v>490.5973598714331</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37356,22 +37356,22 @@
         <v>649</v>
       </c>
       <c r="L35" t="n">
+        <v>235.7435709267094</v>
+      </c>
+      <c r="M35" t="n">
         <v>649</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
-        <v>341.8698541138008</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P35" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37587,25 +37587,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>218.2342914572864</v>
+        <v>221.895519765053</v>
       </c>
       <c r="M38" t="n">
         <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>146.3014272389487</v>
+        <v>649</v>
       </c>
       <c r="O38" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P38" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37727,7 +37727,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>35.46378194444451</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E40" t="n">
         <v>40.01909516304346</v>
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K41" t="n">
+        <v>397.807439363043</v>
+      </c>
+      <c r="L41" t="n">
         <v>649</v>
       </c>
-      <c r="L41" t="n">
-        <v>235.7435709267094</v>
-      </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,22 +38061,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>86.68517751958687</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K44" t="n">
-        <v>175.91191959799</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L44" t="n">
-        <v>218.2342914572864</v>
+        <v>278.5269147425627</v>
       </c>
       <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>649</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
       <c r="O44" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
         <v>198.5777841804241</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
